--- a/data/sample_po.xlsx
+++ b/data/sample_po.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javad\po_matching_app\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B6E955-CB1F-4953-8143-95A10D73702D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -478,11 +489,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,13 +557,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -590,7 +609,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -624,6 +643,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -658,9 +678,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -833,11 +854,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I163"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="18.86328125" customWidth="1"/>
+    <col min="2" max="2" width="21.86328125" customWidth="1"/>
+    <col min="3" max="3" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,7 +893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -892,10 +919,10 @@
         <v>25.35</v>
       </c>
       <c r="I2">
-        <v>2484.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>2484.3000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -924,7 +951,7 @@
         <v>15669.28</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -953,7 +980,7 @@
         <v>254.32</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -982,7 +1009,7 @@
         <v>2777.76</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1011,7 +1038,7 @@
         <v>12196.45</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1040,7 +1067,7 @@
         <v>9972.84</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1069,7 +1096,7 @@
         <v>3415.16</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1098,7 +1125,7 @@
         <v>19019</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1127,7 +1154,7 @@
         <v>3730.2</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1156,7 +1183,7 @@
         <v>50.08</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1182,10 +1209,10 @@
         <v>424.96</v>
       </c>
       <c r="I12">
-        <v>25072.64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>25072.639999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1214,7 +1241,7 @@
         <v>1825.74</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1243,7 +1270,7 @@
         <v>12795.2</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1272,7 +1299,7 @@
         <v>1855.55</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1301,7 +1328,7 @@
         <v>2203.36</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1327,10 +1354,10 @@
         <v>113.65</v>
       </c>
       <c r="I17">
-        <v>5000.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>5000.6000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1359,7 +1386,7 @@
         <v>915.9</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -1388,7 +1415,7 @@
         <v>1879.35</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1414,10 +1441,10 @@
         <v>118.76</v>
       </c>
       <c r="I20">
-        <v>8194.440000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>8194.44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1443,10 +1470,10 @@
         <v>338.56</v>
       </c>
       <c r="I21">
-        <v>19297.92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>19297.919999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1472,10 +1499,10 @@
         <v>51.96</v>
       </c>
       <c r="I22">
-        <v>1143.12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>1143.1199999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1504,7 +1531,7 @@
         <v>11776.32</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1533,7 +1560,7 @@
         <v>3666.08</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -1562,7 +1589,7 @@
         <v>3681.48</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -1588,10 +1615,10 @@
         <v>25.13</v>
       </c>
       <c r="I26">
-        <v>2161.18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>2161.1799999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1620,7 +1647,7 @@
         <v>16606.77</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1649,7 +1676,7 @@
         <v>3190.86</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1675,10 +1702,10 @@
         <v>371.94</v>
       </c>
       <c r="I29">
-        <v>31242.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>31242.959999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1707,7 +1734,7 @@
         <v>4086.6</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -1736,7 +1763,7 @@
         <v>32568.03</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -1765,7 +1792,7 @@
         <v>30412.19</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -1791,10 +1818,10 @@
         <v>112.48</v>
       </c>
       <c r="I33">
-        <v>9673.280000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>9673.2800000000007</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -1823,7 +1850,7 @@
         <v>2850.16</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -1849,10 +1876,10 @@
         <v>22.73</v>
       </c>
       <c r="I35">
-        <v>318.22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>318.22000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -1881,7 +1908,7 @@
         <v>11367</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>22</v>
       </c>
@@ -1910,7 +1937,7 @@
         <v>6960.45</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>22</v>
       </c>
@@ -1939,7 +1966,7 @@
         <v>4771.58</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -1968,7 +1995,7 @@
         <v>11532.64</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>22</v>
       </c>
@@ -1997,7 +2024,7 @@
         <v>30611.7</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -2020,13 +2047,13 @@
         <v>65</v>
       </c>
       <c r="H41">
-        <v>317.15</v>
+        <v>317.14999999999998</v>
       </c>
       <c r="I41">
         <v>20614.75</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -2055,7 +2082,7 @@
         <v>13324.44</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -2084,7 +2111,7 @@
         <v>41078</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -2113,7 +2140,7 @@
         <v>3922.17</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -2142,7 +2169,7 @@
         <v>9981.76</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -2171,7 +2198,7 @@
         <v>2312.31</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -2200,7 +2227,7 @@
         <v>6478.6</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -2229,7 +2256,7 @@
         <v>7806.11</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -2258,7 +2285,7 @@
         <v>11047</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -2287,7 +2314,7 @@
         <v>23263.5</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -2313,10 +2340,10 @@
         <v>23.09</v>
       </c>
       <c r="I51">
-        <v>1246.86</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>1246.8599999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -2345,7 +2372,7 @@
         <v>20680</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -2374,7 +2401,7 @@
         <v>2701.26</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -2403,7 +2430,7 @@
         <v>2770.2</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -2432,7 +2459,7 @@
         <v>449.04</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2461,7 +2488,7 @@
         <v>1813.5</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2490,7 +2517,7 @@
         <v>18189.66</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2519,7 +2546,7 @@
         <v>10866.05</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>27</v>
       </c>
@@ -2548,7 +2575,7 @@
         <v>6787.6</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -2577,7 +2604,7 @@
         <v>8695.92</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -2606,7 +2633,7 @@
         <v>1725.44</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -2629,13 +2656,13 @@
         <v>46</v>
       </c>
       <c r="H62">
-        <v>265.29</v>
+        <v>265.29000000000002</v>
       </c>
       <c r="I62">
         <v>12203.34</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>28</v>
       </c>
@@ -2664,7 +2691,7 @@
         <v>2114.16</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>28</v>
       </c>
@@ -2693,7 +2720,7 @@
         <v>7990</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>28</v>
       </c>
@@ -2722,7 +2749,7 @@
         <v>7435.5</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -2751,7 +2778,7 @@
         <v>5167.54</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -2780,7 +2807,7 @@
         <v>7780.44</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>29</v>
       </c>
@@ -2809,7 +2836,7 @@
         <v>907.24</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -2838,7 +2865,7 @@
         <v>26971.56</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>31</v>
       </c>
@@ -2867,7 +2894,7 @@
         <v>733.12</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>31</v>
       </c>
@@ -2896,7 +2923,7 @@
         <v>2656.32</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>31</v>
       </c>
@@ -2925,7 +2952,7 @@
         <v>1563.42</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>31</v>
       </c>
@@ -2951,10 +2978,10 @@
         <v>109.44</v>
       </c>
       <c r="I73">
-        <v>1094.4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+        <v>1094.4000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>32</v>
       </c>
@@ -2983,7 +3010,7 @@
         <v>5972.84</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>32</v>
       </c>
@@ -3009,10 +3036,10 @@
         <v>370.64</v>
       </c>
       <c r="I75">
-        <v>25944.8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+        <v>25944.799999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>33</v>
       </c>
@@ -3041,7 +3068,7 @@
         <v>2308.6</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>33</v>
       </c>
@@ -3067,10 +3094,10 @@
         <v>327.68</v>
       </c>
       <c r="I77">
-        <v>18350.08</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+        <v>18350.080000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>33</v>
       </c>
@@ -3099,7 +3126,7 @@
         <v>1440.64</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -3128,7 +3155,7 @@
         <v>1239.68</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>35</v>
       </c>
@@ -3157,7 +3184,7 @@
         <v>3088.8</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>35</v>
       </c>
@@ -3186,7 +3213,7 @@
         <v>3700.52</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>35</v>
       </c>
@@ -3215,7 +3242,7 @@
         <v>1972.08</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>35</v>
       </c>
@@ -3244,7 +3271,7 @@
         <v>6071.64</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>36</v>
       </c>
@@ -3273,7 +3300,7 @@
         <v>28411.08</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>36</v>
       </c>
@@ -3302,7 +3329,7 @@
         <v>5240.55</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>36</v>
       </c>
@@ -3328,10 +3355,10 @@
         <v>329.96</v>
       </c>
       <c r="I86">
-        <v>20127.56</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+        <v>20127.560000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>36</v>
       </c>
@@ -3360,7 +3387,7 @@
         <v>5584.84</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>36</v>
       </c>
@@ -3389,7 +3416,7 @@
         <v>14160.54</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>37</v>
       </c>
@@ -3418,7 +3445,7 @@
         <v>4782.46</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>38</v>
       </c>
@@ -3447,7 +3474,7 @@
         <v>9847.17</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -3473,10 +3500,10 @@
         <v>245.92</v>
       </c>
       <c r="I91">
-        <v>983.6799999999999</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
+        <v>983.68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -3502,10 +3529,10 @@
         <v>358.63</v>
       </c>
       <c r="I92">
-        <v>8607.120000000001</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
+        <v>8607.1200000000008</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -3534,7 +3561,7 @@
         <v>9578.68</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -3563,7 +3590,7 @@
         <v>32416.2</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -3589,10 +3616,10 @@
         <v>51.29</v>
       </c>
       <c r="I95">
-        <v>4564.81</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9">
+        <v>4564.8100000000004</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -3621,7 +3648,7 @@
         <v>7837.34</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>41</v>
       </c>
@@ -3650,7 +3677,7 @@
         <v>8632.26</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>41</v>
       </c>
@@ -3676,10 +3703,10 @@
         <v>363.78</v>
       </c>
       <c r="I98">
-        <v>2182.68</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
+        <v>2182.6799999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>41</v>
       </c>
@@ -3705,10 +3732,10 @@
         <v>23.57</v>
       </c>
       <c r="I99">
-        <v>989.9400000000001</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
+        <v>989.94</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>41</v>
       </c>
@@ -3737,7 +3764,7 @@
         <v>4647.78</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>42</v>
       </c>
@@ -3766,7 +3793,7 @@
         <v>18825.13</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>42</v>
       </c>
@@ -3795,7 +3822,7 @@
         <v>21548.25</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>42</v>
       </c>
@@ -3824,7 +3851,7 @@
         <v>19120.5</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>42</v>
       </c>
@@ -3850,10 +3877,10 @@
         <v>21.36</v>
       </c>
       <c r="I104">
-        <v>320.4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
+        <v>320.39999999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>43</v>
       </c>
@@ -3882,7 +3909,7 @@
         <v>26482.68</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>43</v>
       </c>
@@ -3911,7 +3938,7 @@
         <v>20174.75</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>44</v>
       </c>
@@ -3937,10 +3964,10 @@
         <v>122.65</v>
       </c>
       <c r="I107">
-        <v>9444.049999999999</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9">
+        <v>9444.0499999999993</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>44</v>
       </c>
@@ -3969,7 +3996,7 @@
         <v>9484.16</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>45</v>
       </c>
@@ -3998,7 +4025,7 @@
         <v>1428.84</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>45</v>
       </c>
@@ -4027,7 +4054,7 @@
         <v>1503.48</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>45</v>
       </c>
@@ -4050,13 +4077,13 @@
         <v>6</v>
       </c>
       <c r="H111">
-        <v>148.05</v>
+        <v>148.05000000000001</v>
       </c>
       <c r="I111">
         <v>888.3</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>45</v>
       </c>
@@ -4085,7 +4112,7 @@
         <v>186.96</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>45</v>
       </c>
@@ -4111,10 +4138,10 @@
         <v>121.81</v>
       </c>
       <c r="I113">
-        <v>1218.1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9">
+        <v>1218.0999999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>46</v>
       </c>
@@ -4143,7 +4170,7 @@
         <v>2097.48</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>46</v>
       </c>
@@ -4172,7 +4199,7 @@
         <v>23057.32</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>46</v>
       </c>
@@ -4201,7 +4228,7 @@
         <v>2041.6</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>46</v>
       </c>
@@ -4224,13 +4251,13 @@
         <v>72</v>
       </c>
       <c r="H117">
-        <v>259.21</v>
+        <v>259.20999999999998</v>
       </c>
       <c r="I117">
         <v>18663.12</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -4259,7 +4286,7 @@
         <v>168.56</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>47</v>
       </c>
@@ -4288,7 +4315,7 @@
         <v>1399.75</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>47</v>
       </c>
@@ -4317,7 +4344,7 @@
         <v>3981.25</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>47</v>
       </c>
@@ -4346,7 +4373,7 @@
         <v>199.62</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>48</v>
       </c>
@@ -4372,10 +4399,10 @@
         <v>22.65</v>
       </c>
       <c r="I122">
-        <v>158.55</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9">
+        <v>158.55000000000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>48</v>
       </c>
@@ -4401,10 +4428,10 @@
         <v>318.31</v>
       </c>
       <c r="I123">
-        <v>4774.65</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9">
+        <v>4774.6499999999996</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>48</v>
       </c>
@@ -4433,7 +4460,7 @@
         <v>1101.04</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>48</v>
       </c>
@@ -4462,7 +4489,7 @@
         <v>2192.64</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>48</v>
       </c>
@@ -4488,10 +4515,10 @@
         <v>24.44</v>
       </c>
       <c r="I126">
-        <v>146.64</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9">
+        <v>146.63999999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>49</v>
       </c>
@@ -4517,10 +4544,10 @@
         <v>149.57</v>
       </c>
       <c r="I127">
-        <v>8824.629999999999</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9">
+        <v>8824.6299999999992</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>49</v>
       </c>
@@ -4546,10 +4573,10 @@
         <v>23.06</v>
       </c>
       <c r="I128">
-        <v>1199.12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9">
+        <v>1199.1199999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>49</v>
       </c>
@@ -4578,7 +4605,7 @@
         <v>370.2</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>50</v>
       </c>
@@ -4607,7 +4634,7 @@
         <v>4632.54</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>51</v>
       </c>
@@ -4636,7 +4663,7 @@
         <v>1934.73</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>51</v>
       </c>
@@ -4665,7 +4692,7 @@
         <v>893.52</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>51</v>
       </c>
@@ -4691,10 +4718,10 @@
         <v>53.09</v>
       </c>
       <c r="I133">
-        <v>4194.11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9">
+        <v>4194.1099999999997</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>51</v>
       </c>
@@ -4723,7 +4750,7 @@
         <v>8799.34</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>51</v>
       </c>
@@ -4752,7 +4779,7 @@
         <v>2357.04</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>52</v>
       </c>
@@ -4781,7 +4808,7 @@
         <v>2860.29</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>52</v>
       </c>
@@ -4810,7 +4837,7 @@
         <v>1861.08</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>52</v>
       </c>
@@ -4836,10 +4863,10 @@
         <v>114.9</v>
       </c>
       <c r="I138">
-        <v>1263.9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9">
+        <v>1263.9000000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>52</v>
       </c>
@@ -4865,10 +4892,10 @@
         <v>105.95</v>
       </c>
       <c r="I139">
-        <v>317.85</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9">
+        <v>317.85000000000002</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>52</v>
       </c>
@@ -4897,7 +4924,7 @@
         <v>4443.92</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>53</v>
       </c>
@@ -4926,7 +4953,7 @@
         <v>1202.57</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>53</v>
       </c>
@@ -4955,7 +4982,7 @@
         <v>6060</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>53</v>
       </c>
@@ -4984,7 +5011,7 @@
         <v>25458</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>53</v>
       </c>
@@ -5010,10 +5037,10 @@
         <v>52.89</v>
       </c>
       <c r="I144">
-        <v>2538.72</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9">
+        <v>2538.7199999999998</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>53</v>
       </c>
@@ -5042,7 +5069,7 @@
         <v>6346.38</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>54</v>
       </c>
@@ -5071,7 +5098,7 @@
         <v>952.02</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>54</v>
       </c>
@@ -5100,7 +5127,7 @@
         <v>21245.08</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>54</v>
       </c>
@@ -5129,7 +5156,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>54</v>
       </c>
@@ -5155,10 +5182,10 @@
         <v>327.81</v>
       </c>
       <c r="I149">
-        <v>17701.74</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9">
+        <v>17701.740000000002</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>55</v>
       </c>
@@ -5184,10 +5211,10 @@
         <v>468.4</v>
       </c>
       <c r="I150">
-        <v>31851.2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9">
+        <v>31851.200000000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>55</v>
       </c>
@@ -5213,10 +5240,10 @@
         <v>146.72</v>
       </c>
       <c r="I151">
-        <v>880.3200000000001</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9">
+        <v>880.32</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>55</v>
       </c>
@@ -5245,7 +5272,7 @@
         <v>5134.5</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>55</v>
       </c>
@@ -5274,7 +5301,7 @@
         <v>2016.96</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>55</v>
       </c>
@@ -5303,7 +5330,7 @@
         <v>137.46</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>56</v>
       </c>
@@ -5332,7 +5359,7 @@
         <v>1850.07</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>57</v>
       </c>
@@ -5361,7 +5388,7 @@
         <v>9141.76</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>57</v>
       </c>
@@ -5390,7 +5417,7 @@
         <v>1963.08</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>57</v>
       </c>
@@ -5419,7 +5446,7 @@
         <v>11531.7</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -5448,7 +5475,7 @@
         <v>452.2</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -5474,10 +5501,10 @@
         <v>260.33</v>
       </c>
       <c r="I160">
-        <v>1301.65</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9">
+        <v>1301.6500000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -5506,7 +5533,7 @@
         <v>4874.08</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -5529,13 +5556,13 @@
         <v>91</v>
       </c>
       <c r="H162">
-        <v>143.98</v>
+        <v>143.97999999999999</v>
       </c>
       <c r="I162">
         <v>13102.18</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -5566,5 +5593,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>